--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.23.0</t>
+          <t>v0.23.1</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,11 @@
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
@@ -1799,18 +1803,18 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr">
         <is>
           <t>A1, A2, 1, 3, I, IA</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr">
-        <is>
-          <t>4I, 2II</t>
-        </is>
-      </c>
+      <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
@@ -1874,18 +1878,18 @@
       </c>
       <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
           <t>A1, A2, 1, 3, I, IA</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>4I, 2II, 2I</t>
-        </is>
-      </c>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
@@ -1943,7 +1947,11 @@
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1952,11 +1960,7 @@
           <t>A1, A2, 1, 5, II</t>
         </is>
       </c>
-      <c r="S9" s="12" t="inlineStr">
-        <is>
-          <t>6, D3</t>
-        </is>
-      </c>
+      <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
@@ -2010,7 +2014,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -2069,7 +2077,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -2078,11 +2090,7 @@
           <t>A1, A2, 1, 5, III</t>
         </is>
       </c>
-      <c r="S11" s="12" t="inlineStr">
-        <is>
-          <t>6, D3</t>
-        </is>
-      </c>
+      <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
@@ -2132,7 +2140,11 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -2259,7 +2271,11 @@
       </c>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
@@ -2267,11 +2283,7 @@
           <t>D1, 2I, 2II, 4I, IA, I</t>
         </is>
       </c>
-      <c r="S14" s="12" t="inlineStr">
-        <is>
-          <t>3, 1</t>
-        </is>
-      </c>
+      <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
@@ -2326,7 +2338,11 @@
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
@@ -2384,20 +2400,24 @@
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
           <t>D1, 2I, 4II, D3, 6, II</t>
         </is>
       </c>
-      <c r="S16" s="12" t="inlineStr">
-        <is>
-          <t>5, 1</t>
-        </is>
-      </c>
+      <c r="S16" s="12" t="inlineStr"/>
       <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
@@ -2447,7 +2467,11 @@
       <c r="K17" s="12" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -2510,20 +2534,24 @@
           <t>5</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
           <t>D1, 2I, 4II, D3, 6, III</t>
         </is>
       </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>5, 1</t>
-        </is>
-      </c>
+      <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
@@ -2577,7 +2605,11 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -5556,7 +5588,11 @@
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -5619,7 +5655,11 @@
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -5683,7 +5723,11 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -5750,7 +5794,11 @@
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
@@ -5813,7 +5861,11 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -5880,7 +5932,11 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
@@ -6064,7 +6120,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -6131,7 +6191,11 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -6190,7 +6254,11 @@
       </c>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -6253,7 +6321,11 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -9226,7 +9298,11 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -9235,11 +9311,7 @@
           <t>A3, 2II, 4I, IA, I</t>
         </is>
       </c>
-      <c r="S6" s="12" t="inlineStr">
-        <is>
-          <t>3, 1</t>
-        </is>
-      </c>
+      <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
@@ -9289,7 +9361,11 @@
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -9352,20 +9428,24 @@
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
           <t>A3, 2II, 4I, 4II, D3, 6, II</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>5, 1</t>
-        </is>
-      </c>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
@@ -9419,7 +9499,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -9482,20 +9566,24 @@
           <t>5</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
           <t>A3, 2II, 4I, 4II, D3, 6, III</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>5, 1</t>
-        </is>
-      </c>
+      <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
@@ -9549,7 +9637,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -12696,7 +12788,11 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -12767,7 +12863,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -12830,7 +12930,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -12897,7 +13001,11 @@
       <c r="K9" s="12" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -12964,7 +13072,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -13035,7 +13147,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -16292,7 +16408,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -16351,7 +16471,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -16406,7 +16530,11 @@
       <c r="K10" s="12" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -16465,7 +16593,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4II</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -16638,7 +16770,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -16693,7 +16829,11 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -16748,7 +16888,11 @@
       <c r="K16" s="12" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -16808,7 +16952,11 @@
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
@@ -16867,7 +17015,11 @@
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
@@ -19806,7 +19958,11 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -19861,7 +20017,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -20035,7 +20195,11 @@
       </c>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
@@ -20098,7 +20262,11 @@
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
@@ -23910,191 +24078,191 @@
       </c>
       <c r="C17" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OL_delay_dist_weight 0.18
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE A IV
+</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    A3 39444 39146
+</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OL_delay_dist_bias 15
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWP S10/M10
+</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D1 39444 39169
+</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARC_delay_dist_weight 0.08
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 3
+</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWIS
+</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI C1
+</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1 38076 38148
+</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE B I
+</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3 38138 38189
+</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_min_delay 60
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWP S4/M4
+</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5 38177 38228
+</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_max_delay 255
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE C 1
+</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2I 39149 39094
+</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_multiple 5
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NDZ IV
+</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2II 39077 39132
+</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_down_allowed False
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC 5
+</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4I 39045 38990
+</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">shunt_sig_filters_fp True
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE A IV
-</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    A3 39444 39146
-</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_weight 0.18
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWP S10/M10
-</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D1 39444 39169
-</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_bias 15
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 3
-</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SWIS
-</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARC_delay_dist_weight 0.08
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI C1
-</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1 38076 38148
-</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE B I
-</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    3 38138 38189
-</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWP S4/M4
-</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    5 38177 38228
-</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_min_delay 60
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE C 1
-</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2I 39149 39094
-</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_max_delay 255
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NDZ IV
-</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2II 39077 39132
-</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_multiple 5
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEC 5
-</t>
-        </is>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    4I 39045 38990
-</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_down_allowed False
-</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
@@ -24108,7 +24276,12 @@
 </t>
         </is>
       </c>
-      <c r="C27" s="41" t="n"/>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vital_fp_threshold 6
+</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
@@ -24123,7 +24296,12 @@
 </t>
         </is>
       </c>
-      <c r="C28" s="41" t="n"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sub_vital_fp_threshold 50
+</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -24138,7 +24316,12 @@
 </t>
         </is>
       </c>
-      <c r="C29" s="41" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remote_fp_threshold 150
+</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.23.1</t>
+          <t>v0.24.1</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,11 @@
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -1814,12 +1818,28 @@
           <t>A1, A2, 1, 3, I, IA</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr"/>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>4I, 2II</t>
+        </is>
+      </c>
       <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="11" t="inlineStr"/>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
       <c r="AA7" s="13" t="inlineStr"/>
@@ -1889,13 +1909,29 @@
           <t>A1, A2, 1, 3, I, IA</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>4I, 2II, 2I</t>
+        </is>
+      </c>
       <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr"/>
-      <c r="Y8" s="12" t="inlineStr"/>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>A3, 4II</t>
+        </is>
+      </c>
+      <c r="Y8" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="Z8" s="11" t="inlineStr"/>
       <c r="AA8" s="13" t="inlineStr"/>
     </row>
@@ -1960,7 +1996,11 @@
           <t>A1, A2, 1, 5, II</t>
         </is>
       </c>
-      <c r="S9" s="12" t="inlineStr"/>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>6, D3</t>
+        </is>
+      </c>
       <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
@@ -2090,7 +2130,11 @@
           <t>A1, A2, 1, 5, III</t>
         </is>
       </c>
-      <c r="S11" s="12" t="inlineStr"/>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>6, D3</t>
+        </is>
+      </c>
       <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
@@ -2214,7 +2258,11 @@
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
@@ -2283,12 +2331,28 @@
           <t>D1, 2I, 2II, 4I, IA, I</t>
         </is>
       </c>
-      <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>3, 1</t>
+        </is>
+      </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
-      <c r="X14" s="11" t="inlineStr"/>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y14" s="12" t="inlineStr"/>
       <c r="Z14" s="11" t="inlineStr"/>
       <c r="AA14" s="13" t="inlineStr"/>
@@ -2347,8 +2411,16 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
@@ -2417,11 +2489,23 @@
           <t>D1, 2I, 4II, D3, 6, II</t>
         </is>
       </c>
-      <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="12" t="inlineStr"/>
+      <c r="W16" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="11" t="inlineStr"/>
@@ -2477,7 +2561,11 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
@@ -2551,11 +2639,23 @@
           <t>D1, 2I, 4II, D3, 6, III</t>
         </is>
       </c>
-      <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="12" t="inlineStr"/>
+      <c r="W18" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="11" t="inlineStr"/>
@@ -2615,7 +2715,11 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -2679,7 +2783,11 @@
       </c>
       <c r="S20" s="12" t="inlineStr"/>
       <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr"/>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
       <c r="X20" s="11" t="inlineStr"/>
@@ -2742,7 +2850,11 @@
       <c r="R21" s="11" t="inlineStr"/>
       <c r="S21" s="12" t="inlineStr"/>
       <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="12" t="inlineStr"/>
+      <c r="U21" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V21" s="11" t="inlineStr"/>
       <c r="W21" s="12" t="inlineStr"/>
       <c r="X21" s="11" t="inlineStr"/>
@@ -5602,8 +5714,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -5665,8 +5785,16 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -5736,8 +5864,16 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -5803,8 +5939,16 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -5874,8 +6018,16 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -5941,8 +6093,16 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
@@ -6005,7 +6165,11 @@
       </c>
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
@@ -6064,7 +6228,11 @@
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
@@ -9311,12 +9479,28 @@
           <t>A3, 2II, 4I, IA, I</t>
         </is>
       </c>
-      <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>3, 1</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
-      <c r="X6" s="11" t="inlineStr"/>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
       <c r="AA6" s="13" t="inlineStr"/>
@@ -9371,8 +9555,16 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -9445,11 +9637,27 @@
           <t>A3, 2II, 4I, 4II, D3, 6, II</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
       <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
-      <c r="W8" s="12" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
       <c r="Z8" s="11" t="inlineStr"/>
@@ -9510,8 +9718,16 @@
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -9583,11 +9799,27 @@
           <t>A3, 2II, 4I, 4II, D3, 6, III</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
       <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="12" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
@@ -9648,8 +9880,16 @@
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -12803,8 +13043,16 @@
       </c>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>A3, 4II</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
@@ -12874,8 +13122,16 @@
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>A3, 4II</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
@@ -12944,9 +13200,21 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -13011,9 +13279,21 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -13086,9 +13366,21 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -13157,9 +13449,21 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -16301,7 +16605,11 @@
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -16360,7 +16668,11 @@
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -16482,8 +16794,16 @@
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>A3, 4II</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -16540,9 +16860,21 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -16603,9 +16935,21 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>4II, D3</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -16663,7 +17007,11 @@
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
@@ -16718,7 +17066,11 @@
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
@@ -16898,8 +17250,16 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
@@ -16961,8 +17321,16 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
@@ -17024,8 +17392,16 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.1</t>
+          <t>v0.24.2</t>
         </is>
       </c>
     </row>
@@ -1720,10 +1720,14 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>2II+</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="10" t="inlineStr"/>
       <c r="J6" s="11" t="inlineStr">
@@ -1732,18 +1736,30 @@
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II</t>
+        </is>
+      </c>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>4II</t>
+          <t>4II, 2I</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="12" t="inlineStr"/>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>A1, A2, 1, 3, I, IA</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>4I, 2II</t>
+        </is>
+      </c>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr">
         <is>
@@ -1751,8 +1767,16 @@
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr"/>
-      <c r="X6" s="11" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
       <c r="AA6" s="13" t="inlineStr"/>
@@ -1788,7 +1812,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>2II+</t>
+          <t>2II-</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr"/>
@@ -1801,15 +1825,19 @@
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr"/>
+          <t>4I</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>2II</t>
+        </is>
+      </c>
       <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>4II, 2I</t>
+          <t>4II</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -1820,7 +1848,7 @@
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>4I, 2II</t>
+          <t>4I, 2II, 2I</t>
         </is>
       </c>
       <c r="T7" s="11" t="inlineStr"/>
@@ -1830,17 +1858,17 @@
         </is>
       </c>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="Y7" s="12" t="inlineStr"/>
+          <t>A3, 4II</t>
+        </is>
+      </c>
+      <c r="Y7" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="Z7" s="11" t="inlineStr"/>
       <c r="AA7" s="13" t="inlineStr"/>
     </row>
@@ -1870,14 +1898,10 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>2II-</t>
-        </is>
-      </c>
+          <t>DOS</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
       <c r="I8" s="10" t="inlineStr"/>
       <c r="J8" s="11" t="inlineStr">
@@ -1886,16 +1910,8 @@
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
+      <c r="L8" s="11" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
@@ -1904,16 +1920,8 @@
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>A1, A2, 1, 3, I, IA</t>
-        </is>
-      </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>4I, 2II, 2I</t>
-        </is>
-      </c>
+      <c r="R8" s="11" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr">
         <is>
@@ -1922,16 +1930,8 @@
       </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr">
-        <is>
-          <t>A3, 4II</t>
-        </is>
-      </c>
-      <c r="Y8" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="X8" s="11" t="inlineStr"/>
+      <c r="Y8" s="12" t="inlineStr"/>
       <c r="Z8" s="11" t="inlineStr"/>
       <c r="AA8" s="13" t="inlineStr"/>
     </row>
@@ -2729,142 +2729,62 @@
       <c r="AA19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>S10/M10</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>MAF</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>3, C1</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
-      <c r="Q20" s="12" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr">
-        <is>
-          <t>3, 1, A2, A1</t>
-        </is>
-      </c>
-      <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="12" t="inlineStr"/>
-      <c r="X20" s="11" t="inlineStr"/>
-      <c r="Y20" s="12" t="inlineStr"/>
-      <c r="Z20" s="11" t="inlineStr"/>
-      <c r="AA20" s="13" t="inlineStr">
-        <is>
-          <t>MAF</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="12" t="n"/>
+      <c r="R20" s="11" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="11" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="11" t="n"/>
+      <c r="W20" s="12" t="n"/>
+      <c r="X20" s="11" t="n"/>
+      <c r="Y20" s="12" t="n"/>
+      <c r="Z20" s="11" t="n"/>
+      <c r="AA20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>S10/M10</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>MAF</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>DOS</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>3, C1</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="12" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="12" t="inlineStr"/>
-      <c r="X21" s="11" t="inlineStr"/>
-      <c r="Y21" s="12" t="inlineStr"/>
-      <c r="Z21" s="11" t="inlineStr"/>
-      <c r="AA21" s="13" t="inlineStr">
-        <is>
-          <t>MAF</t>
-        </is>
-      </c>
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="12" t="n"/>
+      <c r="R21" s="11" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="11" t="n"/>
+      <c r="U21" s="12" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="W21" s="12" t="n"/>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="12" t="n"/>
+      <c r="Z21" s="11" t="n"/>
+      <c r="AA21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -5662,7 +5582,7 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -5737,7 +5657,7 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
@@ -5808,7 +5728,7 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -5887,7 +5807,7 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
@@ -5962,7 +5882,7 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -6041,7 +5961,7 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
@@ -6116,16 +6036,16 @@
     </row>
     <row r="12" ht="14.4" customHeight="1">
       <c r="A12" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S10/M10</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -6148,10 +6068,14 @@
       <c r="I12" s="10" t="inlineStr"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>3, 1</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>3, C1</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
@@ -6183,16 +6107,16 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S10/M10</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -6215,10 +6139,14 @@
       <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>3, 1</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>3, C1</t>
+        </is>
+      </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
@@ -6246,16 +6174,16 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S4/M4</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -6278,32 +6206,28 @@
       <c r="I14" s="10" t="inlineStr"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3, 1</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+      <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>5, 1, A2, A1</t>
+          <t>3, 1, A2, A1</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
@@ -6317,16 +6241,16 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S4/M4</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -6349,28 +6273,24 @@
       <c r="I15" s="10" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3, 1</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+      <c r="N15" s="11" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
@@ -6384,16 +6304,16 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S6/M6</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -6414,10 +6334,14 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>5, 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr"/>
@@ -6451,16 +6375,16 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S6/M6</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -6481,10 +6405,14 @@
       <c r="G17" s="10" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
       <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>5, 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr"/>
@@ -6513,62 +6441,134 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="11" t="n"/>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="11" t="n"/>
-      <c r="U18" s="12" t="n"/>
-      <c r="V18" s="11" t="n"/>
-      <c r="W18" s="12" t="n"/>
-      <c r="X18" s="11" t="n"/>
-      <c r="Y18" s="12" t="n"/>
-      <c r="Z18" s="11" t="n"/>
-      <c r="AA18" s="13" t="n"/>
+      <c r="A18" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>S8/M8</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>MAF</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr"/>
+      <c r="M18" s="12" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr"/>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>5, 1, A2, A1</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr"/>
+      <c r="U18" s="12" t="inlineStr"/>
+      <c r="V18" s="11" t="inlineStr"/>
+      <c r="W18" s="12" t="inlineStr"/>
+      <c r="X18" s="11" t="inlineStr"/>
+      <c r="Y18" s="12" t="inlineStr"/>
+      <c r="Z18" s="11" t="inlineStr"/>
+      <c r="AA18" s="13" t="inlineStr">
+        <is>
+          <t>MAF</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="12" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="12" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="11" t="n"/>
-      <c r="U19" s="12" t="n"/>
-      <c r="V19" s="11" t="n"/>
-      <c r="W19" s="12" t="n"/>
-      <c r="X19" s="11" t="n"/>
-      <c r="Y19" s="12" t="n"/>
-      <c r="Z19" s="11" t="n"/>
-      <c r="AA19" s="13" t="n"/>
+      <c r="A19" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>S8/M8</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>MAF</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>DOS</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>5, 1</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="12" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr"/>
+      <c r="U19" s="12" t="inlineStr"/>
+      <c r="V19" s="11" t="inlineStr"/>
+      <c r="W19" s="12" t="inlineStr"/>
+      <c r="X19" s="11" t="inlineStr"/>
+      <c r="Y19" s="12" t="inlineStr"/>
+      <c r="Z19" s="11" t="inlineStr"/>
+      <c r="AA19" s="13" t="inlineStr">
+        <is>
+          <t>MAF</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.2</t>
+          <t>v1.0.0</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,11 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr">
         <is>
@@ -1767,16 +1771,8 @@
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="W6" s="12" t="inlineStr"/>
+      <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
       <c r="AA6" s="13" t="inlineStr"/>
@@ -1833,7 +1829,11 @@
           <t>2II</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
@@ -1912,7 +1912,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
@@ -2001,7 +2005,11 @@
           <t>6, D3</t>
         </is>
       </c>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -2064,7 +2072,11 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -2135,7 +2147,11 @@
           <t>6, D3</t>
         </is>
       </c>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -2194,7 +2210,11 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
@@ -2319,12 +2339,12 @@
       </c>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
@@ -2402,12 +2422,12 @@
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
@@ -2494,11 +2514,7 @@
           <t>5, 1</t>
         </is>
       </c>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr">
@@ -2561,11 +2577,7 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T17" s="11" t="inlineStr"/>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
@@ -2644,11 +2656,7 @@
           <t>5, 1</t>
         </is>
       </c>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr">
@@ -2715,11 +2723,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T19" s="11" t="inlineStr"/>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -5634,16 +5638,8 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -5705,16 +5701,8 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -5771,11 +5759,7 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -5850,11 +5834,7 @@
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
@@ -5925,11 +5905,7 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -6004,11 +5980,7 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
@@ -6212,7 +6184,11 @@
       <c r="K14" s="12" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -6279,7 +6255,11 @@
       <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -6360,7 +6340,11 @@
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -6427,7 +6411,11 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
@@ -6494,7 +6482,11 @@
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
@@ -6557,7 +6549,11 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -9472,7 +9468,11 @@
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
@@ -9484,16 +9484,8 @@
           <t>3, 1</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr">
@@ -9551,20 +9543,16 @@
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -9620,11 +9608,7 @@
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
@@ -9642,17 +9626,17 @@
           <t>5, 1</t>
         </is>
       </c>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr">
         <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
           <t>D1</t>
         </is>
       </c>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr">
         <is>
           <t>3</t>
@@ -9707,27 +9691,23 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="N9" s="11" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
           <t>D1</t>
         </is>
       </c>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -9782,11 +9762,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="N10" s="11" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr">
         <is>
@@ -9804,17 +9780,17 @@
           <t>5, 1</t>
         </is>
       </c>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr">
         <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
           <t>D1</t>
         </is>
       </c>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr">
         <is>
           <t>3</t>
@@ -9869,27 +9845,23 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr">
         <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
           <t>D1</t>
         </is>
       </c>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -13028,11 +13000,7 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -13042,17 +13010,17 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="U6" s="12" t="inlineStr">
         <is>
-          <t>A3, 4II</t>
-        </is>
-      </c>
-      <c r="V6" s="11" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+          <t>D3, A3</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
@@ -13111,27 +13079,23 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="U7" s="12" t="inlineStr">
         <is>
-          <t>A3, 4II</t>
-        </is>
-      </c>
-      <c r="V7" s="11" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+          <t>D3, A3</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
@@ -13188,7 +13152,7 @@
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr"/>
@@ -13200,21 +13164,9 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr"/>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -13271,7 +13223,7 @@
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr"/>
@@ -13279,21 +13231,9 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -13354,7 +13294,7 @@
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
@@ -13366,21 +13306,9 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -13441,7 +13369,7 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
@@ -13449,21 +13377,9 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U11" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T11" s="11" t="inlineStr"/>
+      <c r="U11" s="12" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -16598,7 +16514,11 @@
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -16783,27 +16703,23 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="N9" s="11" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>A3, 4II</t>
-        </is>
-      </c>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+          <t>D3, A3</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -16852,7 +16768,7 @@
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
@@ -16860,21 +16776,9 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -16927,7 +16831,7 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>4I, 2II, 4II</t>
+          <t>4I, 2II</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
@@ -16935,21 +16839,9 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>2II</t>
-        </is>
-      </c>
-      <c r="U11" s="12" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>4II, D3</t>
-        </is>
-      </c>
+      <c r="T11" s="11" t="inlineStr"/>
+      <c r="U11" s="12" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -17059,7 +16951,11 @@
       <c r="K13" s="12" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -17132,7 +17028,11 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -17191,7 +17091,11 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -17250,16 +17154,8 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
@@ -17312,11 +17208,7 @@
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
@@ -17383,11 +17275,7 @@
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
@@ -20344,7 +20232,11 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -20403,7 +20295,11 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.1</t>
         </is>
       </c>
     </row>

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -23986,7 +23986,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">

--- a/stations/output/MAL_Interlocking_Program.xlsx
+++ b/stations/output/MAL_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Malveira (MAL)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>Malveira (NOT REAL DATA - FOR TESTING ONLY) (MAL)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha do Oeste</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -1756,7 +1764,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1, 3, I, IA</t>
+          <t>A1, A2, 1, 3, LI, IA</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
@@ -1843,7 +1851,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1, 3, I, IA</t>
+          <t>A1, A2, 1, 3, LI, IA</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr">
@@ -1960,7 +1968,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -1997,7 +2005,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1, 5, II</t>
+          <t>A1, A2, 1, 5, LII</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -2139,7 +2147,7 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1, 5, III</t>
+          <t>A1, A2, 1, 5, LIII</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
@@ -2181,7 +2189,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -2306,12 +2314,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -2348,7 +2356,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 2II, 4I, IA, I</t>
+          <t>D1, 2I, 2II, 4I, IA, LI</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr">
@@ -2393,12 +2401,12 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -2464,12 +2472,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -2506,7 +2514,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 6, II</t>
+          <t>D1, 2I, 4II, D3, 6, LII</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr">
@@ -2543,12 +2551,12 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -2602,12 +2610,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -2648,7 +2656,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 6, III</t>
+          <t>D1, 2I, 4II, D3, 6, LIII</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr">
@@ -2685,12 +2693,12 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -5275,310 +5283,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -5725,7 +5733,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -5871,7 +5879,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -5946,7 +5954,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -6150,12 +6158,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -6221,12 +6229,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -6288,12 +6296,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -6363,12 +6371,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -6434,12 +6442,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -6505,12 +6513,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -9109,310 +9117,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -9434,12 +9442,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -9476,7 +9484,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, IA, I</t>
+          <t>A3, 2II, 4I, IA, LI</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
@@ -9513,12 +9521,12 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -9576,12 +9584,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -9618,7 +9626,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 6, II</t>
+          <t>A3, 2II, 4I, 4II, D3, 6, LII</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr">
@@ -9663,12 +9671,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -9730,12 +9738,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -9772,7 +9780,7 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 6, III</t>
+          <t>A3, 2II, 4I, 4II, D3, 6, LIII</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr">
@@ -9817,12 +9825,12 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -12643,310 +12651,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -13117,7 +13125,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -13188,7 +13196,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -13255,7 +13263,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -13330,7 +13338,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -16165,310 +16173,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -16616,12 +16624,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -16737,7 +16745,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -16796,7 +16804,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -16917,12 +16925,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -16980,12 +16988,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -17047,12 +17055,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -17174,7 +17182,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -17241,7 +17249,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -19869,310 +19877,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -20199,7 +20207,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -20266,7 +20274,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -20324,12 +20332,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -20379,12 +20387,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -23320,24 +23328,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -23345,27 +23353,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -23400,7 +23408,7 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
@@ -23408,7 +23416,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="D4" s="12" t="n">
@@ -23426,7 +23434,7 @@
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
@@ -23434,7 +23442,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -23452,7 +23460,7 @@
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LIII</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -23460,7 +23468,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -23468,7 +23476,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>S4/M4</t>
+          <t>S40/M40</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
@@ -23494,7 +23502,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>S6/M6</t>
+          <t>S60/M60</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
@@ -23546,7 +23554,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>S8/M8</t>
+          <t>S80/M80</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
@@ -24016,7 +24024,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name Malveira
+          <t xml:space="preserve">station_name Malveira (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -24030,7 +24038,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A1 37729 37504
+          <t xml:space="preserve">    A1 737729 737504
 </t>
         </is>
       </c>
@@ -24056,7 +24064,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A2 38056 37729
+          <t xml:space="preserve">    A2 738056 737729
 </t>
         </is>
       </c>
@@ -24082,7 +24090,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1 38118 38157 38056
+          <t xml:space="preserve">    1 738118 738157 738056
 </t>
         </is>
       </c>
@@ -24108,7 +24116,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 38195 38237 38118
+          <t xml:space="preserve">    3 738195 738237 738118
 </t>
         </is>
       </c>
@@ -24134,7 +24142,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 38234 38234 38157
+          <t xml:space="preserve">    5 738234 738234 738157
 </t>
         </is>
       </c>
@@ -24155,7 +24163,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 38606 38237
+          <t xml:space="preserve">    LI 738606 738237
 </t>
         </is>
       </c>
@@ -24176,7 +24184,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 38539 38234
+          <t xml:space="preserve">    LII 738539 738234
 </t>
         </is>
       </c>
@@ -24197,7 +24205,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    III 38539 38234
+          <t xml:space="preserve">    LIII 738539 738234
 </t>
         </is>
       </c>
@@ -24218,7 +24226,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 38625 38539 38539
+          <t xml:space="preserve">    6 738625 738539 738539
 </t>
         </is>
       </c>
@@ -24239,7 +24247,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D3 38954 38625
+          <t xml:space="preserve">    D3 738954 738625
 </t>
         </is>
       </c>
@@ -24260,7 +24268,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IA 38975 38606
+          <t xml:space="preserve">    IA 738975 738606
 </t>
         </is>
       </c>
@@ -24281,7 +24289,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4I 39061 39009 38975
+          <t xml:space="preserve">    4I 739061 739009 738975
 </t>
         </is>
       </c>
@@ -24302,7 +24310,7 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4II 39009 39061 38954
+          <t xml:space="preserve">    4II 739009 739061 738954
 </t>
         </is>
       </c>
@@ -24323,7 +24331,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2II 39146 39112 39061
+          <t xml:space="preserve">    2II 739146 739112 739061
 </t>
         </is>
       </c>
@@ -24344,7 +24352,7 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2I 39169 39061 39112
+          <t xml:space="preserve">    2I 739169 739061 739112
 </t>
         </is>
       </c>
@@ -24364,7 +24372,7 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A3 39444 39146
+          <t xml:space="preserve">    A3 739444 739146
 </t>
         </is>
       </c>
@@ -24384,7 +24392,7 @@
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D1 39444 39169
+          <t xml:space="preserve">    D1 739444 739169
 </t>
         </is>
       </c>
@@ -24424,7 +24432,7 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1 38076 38148
+          <t xml:space="preserve">    1 738076 738148
 </t>
         </is>
       </c>
@@ -24438,13 +24446,13 @@
     <row r="22">
       <c r="A22" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B I
+          <t xml:space="preserve">    NDE B LI
 </t>
         </is>
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 38138 38189
+          <t xml:space="preserve">    3 738138 738189
 </t>
         </is>
       </c>
@@ -24458,13 +24466,13 @@
     <row r="23">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S4/M4
+          <t xml:space="preserve">        SWP S40/M40
 </t>
         </is>
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 38177 38228
+          <t xml:space="preserve">    5 738177 738228
 </t>
         </is>
       </c>
@@ -24484,7 +24492,7 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2I 39149 39094
+          <t xml:space="preserve">    2I 739149 739094
 </t>
         </is>
       </c>
@@ -24504,7 +24512,7 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2II 39077 39132
+          <t xml:space="preserve">    2II 739077 739132
 </t>
         </is>
       </c>
@@ -24524,7 +24532,7 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4I 39045 38990
+          <t xml:space="preserve">    4I 739045 738990
 </t>
         </is>
       </c>
@@ -24538,13 +24546,13 @@
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A II
+          <t xml:space="preserve">    NDE A LII
 </t>
         </is>
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4II 38974 39029
+          <t xml:space="preserve">    4II 738974 739029
 </t>
         </is>
       </c>
@@ -24558,13 +24566,13 @@
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S6/M6
+          <t xml:space="preserve">        SWP S60/M60
 </t>
         </is>
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 38605 38554
+          <t xml:space="preserve">    6 738605 738554
 </t>
         </is>
       </c>
@@ -24578,13 +24586,13 @@
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B III
+          <t xml:space="preserve">    NDE B LIII
 </t>
         </is>
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C1 38196
+          <t xml:space="preserve">    C1 738196
 </t>
         </is>
       </c>
@@ -24598,7 +24606,7 @@
     <row r="30">
       <c r="A30" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S8/M8
+          <t xml:space="preserve">        SWP S80/M80
 </t>
         </is>
       </c>
@@ -24619,7 +24627,7 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 37496 36085 350
+          <t xml:space="preserve">    S1 737496 736085 350
 </t>
         </is>
       </c>
@@ -24634,7 +24642,7 @@
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_A1 37729
+          <t xml:space="preserve">    M_A1 737729
 </t>
         </is>
       </c>
@@ -24642,13 +24650,13 @@
     <row r="33">
       <c r="A33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC I
+          <t xml:space="preserve">SEC LI
 </t>
         </is>
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M1 38055
+          <t xml:space="preserve">    M1 738055
 </t>
         </is>
       </c>
@@ -24662,7 +24670,7 @@
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S10/M10 38203
+          <t xml:space="preserve">    S10/M10 738203
 </t>
         </is>
       </c>
@@ -24676,7 +24684,7 @@
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S8/M8 38239 41012 350
+          <t xml:space="preserve">    S80/M80 738239 741012 350
 </t>
         </is>
       </c>
@@ -24684,13 +24692,13 @@
     <row r="36">
       <c r="A36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC II
+          <t xml:space="preserve">SEC LII
 </t>
         </is>
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 38239 39444 350
+          <t xml:space="preserve">    S60/M60 738239 739444 350
 </t>
         </is>
       </c>
@@ -24704,7 +24712,7 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 38242 41012 350
+          <t xml:space="preserve">    S40/M40 738242 741012 350
 </t>
         </is>
       </c>
@@ -24718,7 +24726,7 @@
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S7/M7 38534 36085 350
+          <t xml:space="preserve">    S7/M7 738534 736085 350
 </t>
         </is>
       </c>
@@ -24726,13 +24734,13 @@
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC III
+          <t xml:space="preserve">SEC LIII
 </t>
         </is>
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5/M5 38534 36085 350
+          <t xml:space="preserve">    S5/M5 738534 736085 350
 </t>
         </is>
       </c>
@@ -24746,7 +24754,7 @@
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M2 38626
+          <t xml:space="preserve">    M2 738626
 </t>
         </is>
       </c>
@@ -24760,7 +24768,7 @@
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3/M3 38970 37504 350
+          <t xml:space="preserve">    S3/M3 738970 737504 350
 </t>
         </is>
       </c>
@@ -24774,7 +24782,7 @@
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_D1 39169
+          <t xml:space="preserve">    M_D1 739169
 </t>
         </is>
       </c>
@@ -24788,7 +24796,7 @@
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_BSP1 39419
+          <t xml:space="preserve">    M_BSP1 739419
 </t>
         </is>
       </c>
@@ -24802,7 +24810,7 @@
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M12 39062
+          <t xml:space="preserve">    M12 739062
 </t>
         </is>
       </c>
@@ -24810,13 +24818,13 @@
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B III
+          <t xml:space="preserve">    NDE B LIII
 </t>
         </is>
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 39451 41012 350
+          <t xml:space="preserve">    S2 739451 741012 350
 </t>
         </is>
       </c>
@@ -24830,7 +24838,7 @@
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SC2 39451 41012 350
+          <t xml:space="preserve">    SC2 739451 741012 350
 </t>
         </is>
       </c>
@@ -24847,7 +24855,7 @@
     <row r="48">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE C II
+          <t xml:space="preserve">    NDE C LII
 </t>
         </is>
       </c>
@@ -24883,7 +24891,7 @@
     <row r="52">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B I
+          <t xml:space="preserve">    NDE B LI
 </t>
         </is>
       </c>
